--- a/R_analysis/output/tables/Tabela_Joinpoint_Completa.xlsx
+++ b/R_analysis/output/tables/Tabela_Joinpoint_Completa.xlsx
@@ -424,7 +424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional (taxa)</t>
+          <t>Brasil — Gestational (taxa)</t>
         </is>
       </c>
       <c r="B2">
@@ -466,7 +466,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional (taxa)</t>
+          <t>Brasil — Gestational (taxa)</t>
         </is>
       </c>
       <c r="B3">
@@ -505,7 +505,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional (casos)</t>
+          <t>Brasil — Gestational (casos)</t>
         </is>
       </c>
       <c r="B4">
@@ -547,7 +547,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional (casos)</t>
+          <t>Brasil — Gestational (casos)</t>
         </is>
       </c>
       <c r="B5">
@@ -586,7 +586,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (taxa)</t>
+          <t>Brasil — Congenital (taxa)</t>
         </is>
       </c>
       <c r="B6">
@@ -628,7 +628,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (taxa)</t>
+          <t>Brasil — Congenital (taxa)</t>
         </is>
       </c>
       <c r="B7">
@@ -670,7 +670,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (taxa)</t>
+          <t>Brasil — Congenital (taxa)</t>
         </is>
       </c>
       <c r="B8">
@@ -712,7 +712,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (taxa)</t>
+          <t>Brasil — Congenital (taxa)</t>
         </is>
       </c>
       <c r="B9">
@@ -751,7 +751,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (casos)</t>
+          <t>Brasil — Congenital (casos)</t>
         </is>
       </c>
       <c r="B10">
@@ -793,7 +793,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (casos)</t>
+          <t>Brasil — Congenital (casos)</t>
         </is>
       </c>
       <c r="B11">
@@ -835,7 +835,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (casos)</t>
+          <t>Brasil — Congenital (casos)</t>
         </is>
       </c>
       <c r="B12">
@@ -877,7 +877,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (casos)</t>
+          <t>Brasil — Congenital (casos)</t>
         </is>
       </c>
       <c r="B13">
@@ -916,7 +916,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Centro-Oeste — Gestacional</t>
+          <t>Central-West — Gestational</t>
         </is>
       </c>
       <c r="B14">
@@ -958,7 +958,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Centro-Oeste — Gestacional</t>
+          <t>Central-West — Gestational</t>
         </is>
       </c>
       <c r="B15">
@@ -1000,7 +1000,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Centro-Oeste — Gestacional</t>
+          <t>Central-West — Gestational</t>
         </is>
       </c>
       <c r="B16">
@@ -1042,7 +1042,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Centro-Oeste — Gestacional</t>
+          <t>Central-West — Gestational</t>
         </is>
       </c>
       <c r="B17">
@@ -1081,7 +1081,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Centro-Oeste — Congênita</t>
+          <t>Central-West — Congenital</t>
         </is>
       </c>
       <c r="B18">
@@ -1123,7 +1123,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Centro-Oeste — Congênita</t>
+          <t>Central-West — Congenital</t>
         </is>
       </c>
       <c r="B19">
@@ -1165,7 +1165,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Centro-Oeste — Congênita</t>
+          <t>Central-West — Congenital</t>
         </is>
       </c>
       <c r="B20">
@@ -1207,7 +1207,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Centro-Oeste — Congênita</t>
+          <t>Central-West — Congenital</t>
         </is>
       </c>
       <c r="B21">
@@ -1249,7 +1249,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Centro-Oeste — Congênita</t>
+          <t>Central-West — Congenital</t>
         </is>
       </c>
       <c r="B22">
@@ -1288,38 +1288,38 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nordeste — Gestacional</t>
+          <t>North — Gestational</t>
         </is>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23">
-        <v>17.7</v>
+        <v>8.57</v>
       </c>
       <c r="D23">
-        <v>15.56</v>
+        <v>5.79</v>
       </c>
       <c r="E23">
-        <v>19.89</v>
+        <v>11.43</v>
       </c>
       <c r="F23">
         <v>2007</v>
       </c>
       <c r="G23">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="H23">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="I23">
         <v>2</v>
       </c>
       <c r="J23">
-        <v>-28.45359028008828</v>
+        <v>-37.7001250082828</v>
       </c>
       <c r="L23">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1330,38 +1330,38 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nordeste — Gestacional</t>
+          <t>North — Gestational</t>
         </is>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>43.26</v>
+        <v>25.27</v>
       </c>
       <c r="D24">
-        <v>29.53</v>
+        <v>21.04</v>
       </c>
       <c r="E24">
-        <v>58.44</v>
+        <v>29.64</v>
       </c>
       <c r="F24">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="G24">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H24">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="I24">
         <v>2</v>
       </c>
       <c r="J24">
-        <v>-28.45359028008828</v>
+        <v>-37.7001250082828</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1372,23 +1372,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nordeste — Gestacional</t>
+          <t>North — Gestational</t>
         </is>
       </c>
       <c r="B25">
         <v>3</v>
       </c>
       <c r="C25">
-        <v>5.15</v>
+        <v>10.4</v>
       </c>
       <c r="D25">
-        <v>0.51</v>
+        <v>7.57</v>
       </c>
       <c r="E25">
-        <v>9.99</v>
+        <v>13.3</v>
       </c>
       <c r="F25">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="G25">
         <v>2023</v>
@@ -1397,10 +1397,10 @@
         <v>2</v>
       </c>
       <c r="J25">
-        <v>-28.45359028008828</v>
+        <v>-37.7001250082828</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1411,38 +1411,38 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nordeste — Congênita</t>
+          <t>North — Congenital</t>
         </is>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26">
-        <v>6.16</v>
+        <v>-5.34</v>
       </c>
       <c r="D26">
-        <v>-3.34</v>
+        <v>-14.22</v>
       </c>
       <c r="E26">
-        <v>16.6</v>
+        <v>4.46</v>
       </c>
       <c r="F26">
         <v>2007</v>
       </c>
       <c r="G26">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H26">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="I26">
         <v>3</v>
       </c>
       <c r="J26">
-        <v>-28.63757882475545</v>
+        <v>-26.95905024934872</v>
       </c>
       <c r="L26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1453,38 +1453,38 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nordeste — Congênita</t>
+          <t>North — Congenital</t>
         </is>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>24.09</v>
+        <v>18.48</v>
       </c>
       <c r="D27">
-        <v>16.94</v>
+        <v>15.96</v>
       </c>
       <c r="E27">
-        <v>31.67</v>
+        <v>21.05</v>
       </c>
       <c r="F27">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="G27">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="H27">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="I27">
         <v>3</v>
       </c>
       <c r="J27">
-        <v>-28.63757882475545</v>
+        <v>-26.95905024934872</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1495,38 +1495,38 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nordeste — Congênita</t>
+          <t>North — Congenital</t>
         </is>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28">
-        <v>9.949999999999999</v>
+        <v>-4.1</v>
       </c>
       <c r="D28">
-        <v>3.62</v>
+        <v>-13.09</v>
       </c>
       <c r="E28">
-        <v>16.67</v>
+        <v>5.83</v>
       </c>
       <c r="F28">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="G28">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="H28">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="I28">
         <v>3</v>
       </c>
       <c r="J28">
-        <v>-28.63757882475545</v>
+        <v>-26.95905024934872</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1537,23 +1537,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nordeste — Congênita</t>
+          <t>North — Congenital</t>
         </is>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
       <c r="C29">
-        <v>-1.05</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="D29">
-        <v>-4.14</v>
+        <v>-1.57</v>
       </c>
       <c r="E29">
-        <v>2.14</v>
+        <v>19.87</v>
       </c>
       <c r="F29">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="G29">
         <v>2023</v>
@@ -1562,10 +1562,10 @@
         <v>3</v>
       </c>
       <c r="J29">
-        <v>-28.63757882475545</v>
+        <v>-26.95905024934872</v>
       </c>
       <c r="L29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -1576,38 +1576,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Norte — Gestacional</t>
+          <t>Northeast — Gestational</t>
         </is>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>8.57</v>
+        <v>17.7</v>
       </c>
       <c r="D30">
-        <v>5.79</v>
+        <v>15.56</v>
       </c>
       <c r="E30">
-        <v>11.43</v>
+        <v>19.89</v>
       </c>
       <c r="F30">
         <v>2007</v>
       </c>
       <c r="G30">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="H30">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="I30">
         <v>2</v>
       </c>
       <c r="J30">
-        <v>-37.7001250082828</v>
+        <v>-28.45359028008828</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -1618,38 +1618,38 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Norte — Gestacional</t>
+          <t>Northeast — Gestational</t>
         </is>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>25.27</v>
+        <v>43.26</v>
       </c>
       <c r="D31">
-        <v>21.04</v>
+        <v>29.53</v>
       </c>
       <c r="E31">
-        <v>29.64</v>
+        <v>58.44</v>
       </c>
       <c r="F31">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="G31">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H31">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="I31">
         <v>2</v>
       </c>
       <c r="J31">
-        <v>-37.7001250082828</v>
+        <v>-28.45359028008828</v>
       </c>
       <c r="L31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -1660,23 +1660,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Norte — Gestacional</t>
+          <t>Northeast — Gestational</t>
         </is>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32">
-        <v>10.4</v>
+        <v>5.15</v>
       </c>
       <c r="D32">
-        <v>7.57</v>
+        <v>0.51</v>
       </c>
       <c r="E32">
-        <v>13.3</v>
+        <v>9.99</v>
       </c>
       <c r="F32">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G32">
         <v>2023</v>
@@ -1685,10 +1685,10 @@
         <v>2</v>
       </c>
       <c r="J32">
-        <v>-37.7001250082828</v>
+        <v>-28.45359028008828</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Norte — Congênita</t>
+          <t>Northeast — Congenital</t>
         </is>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>-5.34</v>
+        <v>6.16</v>
       </c>
       <c r="D33">
-        <v>-14.22</v>
+        <v>-3.34</v>
       </c>
       <c r="E33">
-        <v>4.46</v>
+        <v>16.6</v>
       </c>
       <c r="F33">
         <v>2007</v>
       </c>
       <c r="G33">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H33">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="I33">
         <v>3</v>
       </c>
       <c r="J33">
-        <v>-26.95905024934872</v>
+        <v>-28.63757882475545</v>
       </c>
       <c r="L33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -1741,38 +1741,38 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Norte — Congênita</t>
+          <t>Northeast — Congenital</t>
         </is>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34">
-        <v>18.48</v>
+        <v>24.09</v>
       </c>
       <c r="D34">
-        <v>15.96</v>
+        <v>16.94</v>
       </c>
       <c r="E34">
-        <v>21.05</v>
+        <v>31.67</v>
       </c>
       <c r="F34">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="G34">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="H34">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="I34">
         <v>3</v>
       </c>
       <c r="J34">
-        <v>-26.95905024934872</v>
+        <v>-28.63757882475545</v>
       </c>
       <c r="L34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -1783,38 +1783,38 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Norte — Congênita</t>
+          <t>Northeast — Congenital</t>
         </is>
       </c>
       <c r="B35">
         <v>3</v>
       </c>
       <c r="C35">
-        <v>-4.1</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D35">
-        <v>-13.09</v>
+        <v>3.62</v>
       </c>
       <c r="E35">
-        <v>5.83</v>
+        <v>16.67</v>
       </c>
       <c r="F35">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="G35">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H35">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="I35">
         <v>3</v>
       </c>
       <c r="J35">
-        <v>-26.95905024934872</v>
+        <v>-28.63757882475545</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -1825,23 +1825,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Norte — Congênita</t>
+          <t>Northeast — Congenital</t>
         </is>
       </c>
       <c r="B36">
         <v>4</v>
       </c>
       <c r="C36">
-        <v>8.619999999999999</v>
+        <v>-1.05</v>
       </c>
       <c r="D36">
-        <v>-1.57</v>
+        <v>-4.14</v>
       </c>
       <c r="E36">
-        <v>19.87</v>
+        <v>2.14</v>
       </c>
       <c r="F36">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="G36">
         <v>2023</v>
@@ -1850,10 +1850,10 @@
         <v>3</v>
       </c>
       <c r="J36">
-        <v>-26.95905024934872</v>
+        <v>-28.63757882475545</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -1864,38 +1864,38 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sudeste — Gestacional</t>
+          <t>South — Gestational</t>
         </is>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>34.53</v>
+        <v>15.71</v>
       </c>
       <c r="D37">
-        <v>31.23</v>
+        <v>7.25</v>
       </c>
       <c r="E37">
-        <v>37.91</v>
+        <v>24.82</v>
       </c>
       <c r="F37">
         <v>2007</v>
       </c>
       <c r="G37">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="H37">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="I37">
         <v>2</v>
       </c>
       <c r="J37">
-        <v>-39.25284945243108</v>
+        <v>-38.10557578372459</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -1906,35 +1906,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sudeste — Gestacional</t>
+          <t>South — Gestational</t>
         </is>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38">
-        <v>23.53</v>
+        <v>41.92</v>
       </c>
       <c r="D38">
-        <v>19.54</v>
+        <v>38.32</v>
       </c>
       <c r="E38">
-        <v>27.65</v>
+        <v>45.6</v>
       </c>
       <c r="F38">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="G38">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="H38">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="I38">
         <v>2</v>
       </c>
       <c r="J38">
-        <v>-39.25284945243108</v>
+        <v>-38.10557578372459</v>
       </c>
       <c r="L38">
         <v>6</v>
@@ -1948,23 +1948,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sudeste — Gestacional</t>
+          <t>South — Gestational</t>
         </is>
       </c>
       <c r="B39">
         <v>3</v>
       </c>
       <c r="C39">
-        <v>7.91</v>
+        <v>8.66</v>
       </c>
       <c r="D39">
-        <v>5.27</v>
+        <v>6.88</v>
       </c>
       <c r="E39">
-        <v>10.62</v>
+        <v>10.48</v>
       </c>
       <c r="F39">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="G39">
         <v>2023</v>
@@ -1973,10 +1973,10 @@
         <v>2</v>
       </c>
       <c r="J39">
-        <v>-39.25284945243108</v>
+        <v>-38.10557578372459</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -1987,38 +1987,38 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sudeste — Congênita</t>
+          <t>South — Congenital</t>
         </is>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40">
-        <v>5.35</v>
+        <v>29.2</v>
       </c>
       <c r="D40">
-        <v>-0.85</v>
+        <v>26.91</v>
       </c>
       <c r="E40">
-        <v>11.94</v>
+        <v>31.53</v>
       </c>
       <c r="F40">
         <v>2007</v>
       </c>
       <c r="G40">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="H40">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40">
-        <v>-43.4425223401408</v>
+        <v>-26.82660993256177</v>
       </c>
       <c r="L40">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2029,38 +2029,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sudeste — Congênita</t>
+          <t>South — Congenital</t>
         </is>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41">
-        <v>30.75</v>
+        <v>-0.38</v>
       </c>
       <c r="D41">
-        <v>23.05</v>
+        <v>-3.4</v>
       </c>
       <c r="E41">
-        <v>38.92</v>
+        <v>2.72</v>
       </c>
       <c r="F41">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="G41">
-        <v>2012</v>
-      </c>
-      <c r="H41">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <v>-43.4425223401408</v>
+        <v>-26.82660993256177</v>
       </c>
       <c r="L41">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2071,35 +2068,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sudeste — Congênita</t>
+          <t>Southeast — Gestational</t>
         </is>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>15.41</v>
+        <v>34.53</v>
       </c>
       <c r="D42">
-        <v>12.32</v>
+        <v>31.23</v>
       </c>
       <c r="E42">
-        <v>18.59</v>
+        <v>37.91</v>
       </c>
       <c r="F42">
+        <v>2007</v>
+      </c>
+      <c r="G42">
         <v>2012</v>
       </c>
-      <c r="G42">
-        <v>2017</v>
-      </c>
       <c r="H42">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J42">
-        <v>-43.4425223401408</v>
+        <v>-39.25284945243108</v>
       </c>
       <c r="L42">
         <v>5</v>
@@ -2113,32 +2110,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sudeste — Congênita</t>
+          <t>Southeast — Gestational</t>
         </is>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>-0.61</v>
+        <v>23.53</v>
       </c>
       <c r="D43">
-        <v>-2.63</v>
+        <v>19.54</v>
       </c>
       <c r="E43">
-        <v>1.45</v>
+        <v>27.65</v>
       </c>
       <c r="F43">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G43">
-        <v>2023</v>
+        <v>2018</v>
+      </c>
+      <c r="H43">
+        <v>2018</v>
       </c>
       <c r="I43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J43">
-        <v>-43.4425223401408</v>
+        <v>-39.25284945243108</v>
       </c>
       <c r="L43">
         <v>6</v>
@@ -2152,38 +2152,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sul — Gestacional</t>
+          <t>Southeast — Gestational</t>
         </is>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>15.71</v>
+        <v>7.91</v>
       </c>
       <c r="D44">
-        <v>7.25</v>
+        <v>5.27</v>
       </c>
       <c r="E44">
-        <v>24.82</v>
+        <v>10.62</v>
       </c>
       <c r="F44">
-        <v>2007</v>
+        <v>2018</v>
       </c>
       <c r="G44">
-        <v>2010</v>
-      </c>
-      <c r="H44">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="I44">
         <v>2</v>
       </c>
       <c r="J44">
-        <v>-38.10557578372459</v>
+        <v>-39.25284945243108</v>
       </c>
       <c r="L44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -2194,38 +2191,38 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sul — Gestacional</t>
+          <t>Southeast — Congenital</t>
         </is>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>41.92</v>
+        <v>5.35</v>
       </c>
       <c r="D45">
-        <v>38.32</v>
+        <v>-0.85</v>
       </c>
       <c r="E45">
-        <v>45.6</v>
+        <v>11.94</v>
       </c>
       <c r="F45">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="G45">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="H45">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="I45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <v>-38.10557578372459</v>
+        <v>-43.4425223401408</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -2236,35 +2233,38 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sul — Gestacional</t>
+          <t>Southeast — Congenital</t>
         </is>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>8.66</v>
+        <v>30.75</v>
       </c>
       <c r="D46">
-        <v>6.88</v>
+        <v>23.05</v>
       </c>
       <c r="E46">
-        <v>10.48</v>
+        <v>38.92</v>
       </c>
       <c r="F46">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="G46">
-        <v>2023</v>
+        <v>2012</v>
+      </c>
+      <c r="H46">
+        <v>2012</v>
       </c>
       <c r="I46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J46">
-        <v>-38.10557578372459</v>
+        <v>-43.4425223401408</v>
       </c>
       <c r="L46">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -2275,38 +2275,38 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sul — Congênita</t>
+          <t>Southeast — Congenital</t>
         </is>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>29.2</v>
+        <v>15.41</v>
       </c>
       <c r="D47">
-        <v>26.91</v>
+        <v>12.32</v>
       </c>
       <c r="E47">
-        <v>31.53</v>
+        <v>18.59</v>
       </c>
       <c r="F47">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="G47">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H47">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J47">
-        <v>-26.82660993256177</v>
+        <v>-43.4425223401408</v>
       </c>
       <c r="L47">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -2317,35 +2317,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sul — Congênita</t>
+          <t>Southeast — Congenital</t>
         </is>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>-0.38</v>
+        <v>-0.61</v>
       </c>
       <c r="D48">
-        <v>-3.4</v>
+        <v>-2.63</v>
       </c>
       <c r="E48">
-        <v>2.72</v>
+        <v>1.45</v>
       </c>
       <c r="F48">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G48">
         <v>2023</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48">
-        <v>-26.82660993256177</v>
+        <v>-43.4425223401408</v>
       </c>
       <c r="L48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RO — Gestacional</t>
+          <t>RO — Gestational</t>
         </is>
       </c>
       <c r="B49">
@@ -2398,7 +2398,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RO — Gestacional</t>
+          <t>RO — Gestational</t>
         </is>
       </c>
       <c r="B50">
@@ -2440,7 +2440,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RO — Gestacional</t>
+          <t>RO — Gestational</t>
         </is>
       </c>
       <c r="B51">
@@ -2482,7 +2482,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RO — Gestacional</t>
+          <t>RO — Gestational</t>
         </is>
       </c>
       <c r="B52">
@@ -2521,7 +2521,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RO — Congênita</t>
+          <t>RO — Congenital</t>
         </is>
       </c>
       <c r="B53">
@@ -2563,7 +2563,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RO — Congênita</t>
+          <t>RO — Congenital</t>
         </is>
       </c>
       <c r="B54">
@@ -2605,7 +2605,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RO — Congênita</t>
+          <t>RO — Congenital</t>
         </is>
       </c>
       <c r="B55">
@@ -2647,7 +2647,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RO — Congênita</t>
+          <t>RO — Congenital</t>
         </is>
       </c>
       <c r="B56">
@@ -2689,7 +2689,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RO — Congênita</t>
+          <t>RO — Congenital</t>
         </is>
       </c>
       <c r="B57">
@@ -2728,7 +2728,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AC — Gestacional</t>
+          <t>AC — Gestational</t>
         </is>
       </c>
       <c r="B58">
@@ -2770,7 +2770,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AC — Gestacional</t>
+          <t>AC — Gestational</t>
         </is>
       </c>
       <c r="B59">
@@ -2812,7 +2812,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AC — Gestacional</t>
+          <t>AC — Gestational</t>
         </is>
       </c>
       <c r="B60">
@@ -2851,7 +2851,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AC — Congênita</t>
+          <t>AC — Congenital</t>
         </is>
       </c>
       <c r="B61">
@@ -2893,7 +2893,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AC — Congênita</t>
+          <t>AC — Congenital</t>
         </is>
       </c>
       <c r="B62">
@@ -2935,7 +2935,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AC — Congênita</t>
+          <t>AC — Congenital</t>
         </is>
       </c>
       <c r="B63">
@@ -2974,7 +2974,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AM — Gestacional</t>
+          <t>AM — Gestational</t>
         </is>
       </c>
       <c r="B64">
@@ -3016,7 +3016,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AM — Gestacional</t>
+          <t>AM — Gestational</t>
         </is>
       </c>
       <c r="B65">
@@ -3058,7 +3058,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AM — Gestacional</t>
+          <t>AM — Gestational</t>
         </is>
       </c>
       <c r="B66">
@@ -3097,7 +3097,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AM — Congênita</t>
+          <t>AM — Congenital</t>
         </is>
       </c>
       <c r="B67">
@@ -3139,7 +3139,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AM — Congênita</t>
+          <t>AM — Congenital</t>
         </is>
       </c>
       <c r="B68">
@@ -3181,7 +3181,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AM — Congênita</t>
+          <t>AM — Congenital</t>
         </is>
       </c>
       <c r="B69">
@@ -3223,7 +3223,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AM — Congênita</t>
+          <t>AM — Congenital</t>
         </is>
       </c>
       <c r="B70">
@@ -3265,7 +3265,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AM — Congênita</t>
+          <t>AM — Congenital</t>
         </is>
       </c>
       <c r="B71">
@@ -3304,7 +3304,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RR — Gestacional</t>
+          <t>RR — Gestational</t>
         </is>
       </c>
       <c r="B72">
@@ -3346,7 +3346,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RR — Gestacional</t>
+          <t>RR — Gestational</t>
         </is>
       </c>
       <c r="B73">
@@ -3388,7 +3388,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RR — Gestacional</t>
+          <t>RR — Gestational</t>
         </is>
       </c>
       <c r="B74">
@@ -3427,7 +3427,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RR — Congênita</t>
+          <t>RR — Congenital</t>
         </is>
       </c>
       <c r="B75">
@@ -3469,7 +3469,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RR — Congênita</t>
+          <t>RR — Congenital</t>
         </is>
       </c>
       <c r="B76">
@@ -3511,7 +3511,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RR — Congênita</t>
+          <t>RR — Congenital</t>
         </is>
       </c>
       <c r="B77">
@@ -3553,7 +3553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RR — Congênita</t>
+          <t>RR — Congenital</t>
         </is>
       </c>
       <c r="B78">
@@ -3592,7 +3592,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PA — Gestacional</t>
+          <t>PA — Gestational</t>
         </is>
       </c>
       <c r="B79">
@@ -3634,7 +3634,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PA — Congênita</t>
+          <t>PA — Congenital</t>
         </is>
       </c>
       <c r="B80">
@@ -3676,7 +3676,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PA — Congênita</t>
+          <t>PA — Congenital</t>
         </is>
       </c>
       <c r="B81">
@@ -3715,7 +3715,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AP — Gestacional</t>
+          <t>AP — Gestational</t>
         </is>
       </c>
       <c r="B82">
@@ -3757,7 +3757,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AP — Gestacional</t>
+          <t>AP — Gestational</t>
         </is>
       </c>
       <c r="B83">
@@ -3796,7 +3796,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AP — Congênita</t>
+          <t>AP — Congenital</t>
         </is>
       </c>
       <c r="B84">
@@ -3838,7 +3838,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AP — Congênita</t>
+          <t>AP — Congenital</t>
         </is>
       </c>
       <c r="B85">
@@ -3880,7 +3880,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AP — Congênita</t>
+          <t>AP — Congenital</t>
         </is>
       </c>
       <c r="B86">
@@ -3919,7 +3919,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TO — Gestacional</t>
+          <t>TO — Gestational</t>
         </is>
       </c>
       <c r="B87">
@@ -3961,7 +3961,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TO — Gestacional</t>
+          <t>TO — Gestational</t>
         </is>
       </c>
       <c r="B88">
@@ -4003,7 +4003,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TO — Gestacional</t>
+          <t>TO — Gestational</t>
         </is>
       </c>
       <c r="B89">
@@ -4045,7 +4045,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TO — Gestacional</t>
+          <t>TO — Gestational</t>
         </is>
       </c>
       <c r="B90">
@@ -4087,7 +4087,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TO — Gestacional</t>
+          <t>TO — Gestational</t>
         </is>
       </c>
       <c r="B91">
@@ -4126,7 +4126,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TO — Congênita</t>
+          <t>TO — Congenital</t>
         </is>
       </c>
       <c r="B92">
@@ -4168,7 +4168,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TO — Congênita</t>
+          <t>TO — Congenital</t>
         </is>
       </c>
       <c r="B93">
@@ -4210,7 +4210,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TO — Congênita</t>
+          <t>TO — Congenital</t>
         </is>
       </c>
       <c r="B94">
@@ -4252,7 +4252,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TO — Congênita</t>
+          <t>TO — Congenital</t>
         </is>
       </c>
       <c r="B95">
@@ -4291,7 +4291,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MA — Gestacional</t>
+          <t>MA — Gestational</t>
         </is>
       </c>
       <c r="B96">
@@ -4333,7 +4333,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MA — Gestacional</t>
+          <t>MA — Gestational</t>
         </is>
       </c>
       <c r="B97">
@@ -4375,7 +4375,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MA — Gestacional</t>
+          <t>MA — Gestational</t>
         </is>
       </c>
       <c r="B98">
@@ -4414,7 +4414,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MA — Congênita</t>
+          <t>MA — Congenital</t>
         </is>
       </c>
       <c r="B99">
@@ -4456,7 +4456,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MA — Congênita</t>
+          <t>MA — Congenital</t>
         </is>
       </c>
       <c r="B100">
@@ -4498,7 +4498,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MA — Congênita</t>
+          <t>MA — Congenital</t>
         </is>
       </c>
       <c r="B101">
@@ -4537,7 +4537,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PI — Gestacional</t>
+          <t>PI — Gestational</t>
         </is>
       </c>
       <c r="B102">
@@ -4579,7 +4579,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PI — Gestacional</t>
+          <t>PI — Gestational</t>
         </is>
       </c>
       <c r="B103">
@@ -4621,7 +4621,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PI — Gestacional</t>
+          <t>PI — Gestational</t>
         </is>
       </c>
       <c r="B104">
@@ -4663,7 +4663,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PI — Gestacional</t>
+          <t>PI — Gestational</t>
         </is>
       </c>
       <c r="B105">
@@ -4705,7 +4705,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PI — Gestacional</t>
+          <t>PI — Gestational</t>
         </is>
       </c>
       <c r="B106">
@@ -4744,7 +4744,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PI — Congênita</t>
+          <t>PI — Congenital</t>
         </is>
       </c>
       <c r="B107">
@@ -4786,7 +4786,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PI — Congênita</t>
+          <t>PI — Congenital</t>
         </is>
       </c>
       <c r="B108">
@@ -4828,7 +4828,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PI — Congênita</t>
+          <t>PI — Congenital</t>
         </is>
       </c>
       <c r="B109">
@@ -4867,7 +4867,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CE — Gestacional</t>
+          <t>CE — Gestational</t>
         </is>
       </c>
       <c r="B110">
@@ -4909,7 +4909,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CE — Congênita</t>
+          <t>CE — Congenital</t>
         </is>
       </c>
       <c r="B111">
@@ -4951,7 +4951,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CE — Congênita</t>
+          <t>CE — Congenital</t>
         </is>
       </c>
       <c r="B112">
@@ -4990,7 +4990,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RN — Gestacional</t>
+          <t>RN — Gestational</t>
         </is>
       </c>
       <c r="B113">
@@ -5032,7 +5032,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RN — Gestacional</t>
+          <t>RN — Gestational</t>
         </is>
       </c>
       <c r="B114">
@@ -5074,7 +5074,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RN — Gestacional</t>
+          <t>RN — Gestational</t>
         </is>
       </c>
       <c r="B115">
@@ -5113,7 +5113,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RN — Congênita</t>
+          <t>RN — Congenital</t>
         </is>
       </c>
       <c r="B116">
@@ -5155,7 +5155,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RN — Congênita</t>
+          <t>RN — Congenital</t>
         </is>
       </c>
       <c r="B117">
@@ -5194,7 +5194,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PB — Gestacional</t>
+          <t>PB — Gestational</t>
         </is>
       </c>
       <c r="B118">
@@ -5236,7 +5236,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PB — Gestacional</t>
+          <t>PB — Gestational</t>
         </is>
       </c>
       <c r="B119">
@@ -5278,7 +5278,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PB — Gestacional</t>
+          <t>PB — Gestational</t>
         </is>
       </c>
       <c r="B120">
@@ -5320,7 +5320,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PB — Gestacional</t>
+          <t>PB — Gestational</t>
         </is>
       </c>
       <c r="B121">
@@ -5359,7 +5359,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PB — Congênita</t>
+          <t>PB — Congenital</t>
         </is>
       </c>
       <c r="B122">
@@ -5398,7 +5398,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PE — Gestacional</t>
+          <t>PE — Gestational</t>
         </is>
       </c>
       <c r="B123">
@@ -5440,7 +5440,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PE — Gestacional</t>
+          <t>PE — Gestational</t>
         </is>
       </c>
       <c r="B124">
@@ -5482,7 +5482,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PE — Gestacional</t>
+          <t>PE — Gestational</t>
         </is>
       </c>
       <c r="B125">
@@ -5524,7 +5524,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PE — Gestacional</t>
+          <t>PE — Gestational</t>
         </is>
       </c>
       <c r="B126">
@@ -5563,7 +5563,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PE — Congênita</t>
+          <t>PE — Congenital</t>
         </is>
       </c>
       <c r="B127">
@@ -5605,7 +5605,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PE — Congênita</t>
+          <t>PE — Congenital</t>
         </is>
       </c>
       <c r="B128">
@@ -5647,7 +5647,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PE — Congênita</t>
+          <t>PE — Congenital</t>
         </is>
       </c>
       <c r="B129">
@@ -5689,7 +5689,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PE — Congênita</t>
+          <t>PE — Congenital</t>
         </is>
       </c>
       <c r="B130">
@@ -5731,7 +5731,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PE — Congênita</t>
+          <t>PE — Congenital</t>
         </is>
       </c>
       <c r="B131">
@@ -5770,7 +5770,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AL — Gestacional</t>
+          <t>AL — Gestational</t>
         </is>
       </c>
       <c r="B132">
@@ -5812,7 +5812,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AL — Gestacional</t>
+          <t>AL — Gestational</t>
         </is>
       </c>
       <c r="B133">
@@ -5854,7 +5854,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AL — Gestacional</t>
+          <t>AL — Gestational</t>
         </is>
       </c>
       <c r="B134">
@@ -5893,7 +5893,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AL — Congênita</t>
+          <t>AL — Congenital</t>
         </is>
       </c>
       <c r="B135">
@@ -5935,7 +5935,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AL — Congênita</t>
+          <t>AL — Congenital</t>
         </is>
       </c>
       <c r="B136">
@@ -5977,7 +5977,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AL — Congênita</t>
+          <t>AL — Congenital</t>
         </is>
       </c>
       <c r="B137">
@@ -6016,7 +6016,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SE — Gestacional</t>
+          <t>SE — Gestational</t>
         </is>
       </c>
       <c r="B138">
@@ -6058,7 +6058,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SE — Gestacional</t>
+          <t>SE — Gestational</t>
         </is>
       </c>
       <c r="B139">
@@ -6100,7 +6100,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SE — Gestacional</t>
+          <t>SE — Gestational</t>
         </is>
       </c>
       <c r="B140">
@@ -6142,7 +6142,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SE — Gestacional</t>
+          <t>SE — Gestational</t>
         </is>
       </c>
       <c r="B141">
@@ -6184,7 +6184,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SE — Gestacional</t>
+          <t>SE — Gestational</t>
         </is>
       </c>
       <c r="B142">
@@ -6223,7 +6223,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SE — Congênita</t>
+          <t>SE — Congenital</t>
         </is>
       </c>
       <c r="B143">
@@ -6265,7 +6265,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SE — Congênita</t>
+          <t>SE — Congenital</t>
         </is>
       </c>
       <c r="B144">
@@ -6307,7 +6307,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SE — Congênita</t>
+          <t>SE — Congenital</t>
         </is>
       </c>
       <c r="B145">
@@ -6349,7 +6349,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SE — Congênita</t>
+          <t>SE — Congenital</t>
         </is>
       </c>
       <c r="B146">
@@ -6391,7 +6391,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SE — Congênita</t>
+          <t>SE — Congenital</t>
         </is>
       </c>
       <c r="B147">
@@ -6430,7 +6430,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BA — Gestacional</t>
+          <t>BA — Gestational</t>
         </is>
       </c>
       <c r="B148">
@@ -6472,7 +6472,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BA — Gestacional</t>
+          <t>BA — Gestational</t>
         </is>
       </c>
       <c r="B149">
@@ -6514,7 +6514,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BA — Gestacional</t>
+          <t>BA — Gestational</t>
         </is>
       </c>
       <c r="B150">
@@ -6553,7 +6553,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BA — Congênita</t>
+          <t>BA — Congenital</t>
         </is>
       </c>
       <c r="B151">
@@ -6595,7 +6595,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BA — Congênita</t>
+          <t>BA — Congenital</t>
         </is>
       </c>
       <c r="B152">
@@ -6637,7 +6637,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BA — Congênita</t>
+          <t>BA — Congenital</t>
         </is>
       </c>
       <c r="B153">
@@ -6676,7 +6676,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MG — Gestacional</t>
+          <t>MG — Gestational</t>
         </is>
       </c>
       <c r="B154">
@@ -6718,7 +6718,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MG — Gestacional</t>
+          <t>MG — Gestational</t>
         </is>
       </c>
       <c r="B155">
@@ -6760,7 +6760,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MG — Gestacional</t>
+          <t>MG — Gestational</t>
         </is>
       </c>
       <c r="B156">
@@ -6802,7 +6802,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MG — Gestacional</t>
+          <t>MG — Gestational</t>
         </is>
       </c>
       <c r="B157">
@@ -6841,7 +6841,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MG — Congênita</t>
+          <t>MG — Congenital</t>
         </is>
       </c>
       <c r="B158">
@@ -6883,7 +6883,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MG — Congênita</t>
+          <t>MG — Congenital</t>
         </is>
       </c>
       <c r="B159">
@@ -6925,7 +6925,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MG — Congênita</t>
+          <t>MG — Congenital</t>
         </is>
       </c>
       <c r="B160">
@@ -6967,7 +6967,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MG — Congênita</t>
+          <t>MG — Congenital</t>
         </is>
       </c>
       <c r="B161">
@@ -7006,7 +7006,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ES — Gestacional</t>
+          <t>ES — Gestational</t>
         </is>
       </c>
       <c r="B162">
@@ -7048,7 +7048,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ES — Gestacional</t>
+          <t>ES — Gestational</t>
         </is>
       </c>
       <c r="B163">
@@ -7090,7 +7090,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ES — Gestacional</t>
+          <t>ES — Gestational</t>
         </is>
       </c>
       <c r="B164">
@@ -7132,7 +7132,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ES — Gestacional</t>
+          <t>ES — Gestational</t>
         </is>
       </c>
       <c r="B165">
@@ -7171,7 +7171,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ES — Congênita</t>
+          <t>ES — Congenital</t>
         </is>
       </c>
       <c r="B166">
@@ -7213,7 +7213,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ES — Congênita</t>
+          <t>ES — Congenital</t>
         </is>
       </c>
       <c r="B167">
@@ -7255,7 +7255,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ES — Congênita</t>
+          <t>ES — Congenital</t>
         </is>
       </c>
       <c r="B168">
@@ -7297,7 +7297,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ES — Congênita</t>
+          <t>ES — Congenital</t>
         </is>
       </c>
       <c r="B169">
@@ -7339,7 +7339,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ES — Congênita</t>
+          <t>ES — Congenital</t>
         </is>
       </c>
       <c r="B170">
@@ -7378,7 +7378,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>RJ — Gestacional</t>
+          <t>RJ — Gestational</t>
         </is>
       </c>
       <c r="B171">
@@ -7420,7 +7420,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>RJ — Gestacional</t>
+          <t>RJ — Gestational</t>
         </is>
       </c>
       <c r="B172">
@@ -7462,7 +7462,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>RJ — Gestacional</t>
+          <t>RJ — Gestational</t>
         </is>
       </c>
       <c r="B173">
@@ -7501,7 +7501,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>RJ — Congênita</t>
+          <t>RJ — Congenital</t>
         </is>
       </c>
       <c r="B174">
@@ -7543,7 +7543,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>RJ — Congênita</t>
+          <t>RJ — Congenital</t>
         </is>
       </c>
       <c r="B175">
@@ -7585,7 +7585,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>RJ — Congênita</t>
+          <t>RJ — Congenital</t>
         </is>
       </c>
       <c r="B176">
@@ -7627,7 +7627,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>RJ — Congênita</t>
+          <t>RJ — Congenital</t>
         </is>
       </c>
       <c r="B177">
@@ -7666,7 +7666,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SP — Gestacional</t>
+          <t>SP — Gestational</t>
         </is>
       </c>
       <c r="B178">
@@ -7708,7 +7708,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SP — Gestacional</t>
+          <t>SP — Gestational</t>
         </is>
       </c>
       <c r="B179">
@@ -7750,7 +7750,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SP — Gestacional</t>
+          <t>SP — Gestational</t>
         </is>
       </c>
       <c r="B180">
@@ -7789,7 +7789,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SP — Congênita</t>
+          <t>SP — Congenital</t>
         </is>
       </c>
       <c r="B181">
@@ -7831,7 +7831,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SP — Congênita</t>
+          <t>SP — Congenital</t>
         </is>
       </c>
       <c r="B182">
@@ -7873,7 +7873,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SP — Congênita</t>
+          <t>SP — Congenital</t>
         </is>
       </c>
       <c r="B183">
@@ -7915,7 +7915,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SP — Congênita</t>
+          <t>SP — Congenital</t>
         </is>
       </c>
       <c r="B184">
@@ -7957,7 +7957,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SP — Congênita</t>
+          <t>SP — Congenital</t>
         </is>
       </c>
       <c r="B185">
@@ -7996,7 +7996,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PR — Gestacional</t>
+          <t>PR — Gestational</t>
         </is>
       </c>
       <c r="B186">
@@ -8038,7 +8038,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PR — Gestacional</t>
+          <t>PR — Gestational</t>
         </is>
       </c>
       <c r="B187">
@@ -8080,7 +8080,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PR — Gestacional</t>
+          <t>PR — Gestational</t>
         </is>
       </c>
       <c r="B188">
@@ -8119,7 +8119,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PR — Congênita</t>
+          <t>PR — Congenital</t>
         </is>
       </c>
       <c r="B189">
@@ -8161,7 +8161,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PR — Congênita</t>
+          <t>PR — Congenital</t>
         </is>
       </c>
       <c r="B190">
@@ -8203,7 +8203,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PR — Congênita</t>
+          <t>PR — Congenital</t>
         </is>
       </c>
       <c r="B191">
@@ -8245,7 +8245,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PR — Congênita</t>
+          <t>PR — Congenital</t>
         </is>
       </c>
       <c r="B192">
@@ -8284,7 +8284,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SC — Gestacional</t>
+          <t>SC — Gestational</t>
         </is>
       </c>
       <c r="B193">
@@ -8326,7 +8326,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SC — Gestacional</t>
+          <t>SC — Gestational</t>
         </is>
       </c>
       <c r="B194">
@@ -8368,7 +8368,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SC — Gestacional</t>
+          <t>SC — Gestational</t>
         </is>
       </c>
       <c r="B195">
@@ -8410,7 +8410,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SC — Gestacional</t>
+          <t>SC — Gestational</t>
         </is>
       </c>
       <c r="B196">
@@ -8452,7 +8452,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SC — Gestacional</t>
+          <t>SC — Gestational</t>
         </is>
       </c>
       <c r="B197">
@@ -8491,7 +8491,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SC — Congênita</t>
+          <t>SC — Congenital</t>
         </is>
       </c>
       <c r="B198">
@@ -8533,7 +8533,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SC — Congênita</t>
+          <t>SC — Congenital</t>
         </is>
       </c>
       <c r="B199">
@@ -8575,7 +8575,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SC — Congênita</t>
+          <t>SC — Congenital</t>
         </is>
       </c>
       <c r="B200">
@@ -8614,7 +8614,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>RS — Gestacional</t>
+          <t>RS — Gestational</t>
         </is>
       </c>
       <c r="B201">
@@ -8656,7 +8656,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>RS — Gestacional</t>
+          <t>RS — Gestational</t>
         </is>
       </c>
       <c r="B202">
@@ -8698,7 +8698,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>RS — Gestacional</t>
+          <t>RS — Gestational</t>
         </is>
       </c>
       <c r="B203">
@@ -8740,7 +8740,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>RS — Gestacional</t>
+          <t>RS — Gestational</t>
         </is>
       </c>
       <c r="B204">
@@ -8779,7 +8779,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>RS — Congênita</t>
+          <t>RS — Congenital</t>
         </is>
       </c>
       <c r="B205">
@@ -8821,7 +8821,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RS — Congênita</t>
+          <t>RS — Congenital</t>
         </is>
       </c>
       <c r="B206">
@@ -8860,7 +8860,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MS — Gestacional</t>
+          <t>MS — Gestational</t>
         </is>
       </c>
       <c r="B207">
@@ -8902,7 +8902,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MS — Gestacional</t>
+          <t>MS — Gestational</t>
         </is>
       </c>
       <c r="B208">
@@ -8944,7 +8944,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MS — Gestacional</t>
+          <t>MS — Gestational</t>
         </is>
       </c>
       <c r="B209">
@@ -8986,7 +8986,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>MS — Gestacional</t>
+          <t>MS — Gestational</t>
         </is>
       </c>
       <c r="B210">
@@ -9025,7 +9025,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>MS — Congênita</t>
+          <t>MS — Congenital</t>
         </is>
       </c>
       <c r="B211">
@@ -9067,7 +9067,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MS — Congênita</t>
+          <t>MS — Congenital</t>
         </is>
       </c>
       <c r="B212">
@@ -9109,7 +9109,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MS — Congênita</t>
+          <t>MS — Congenital</t>
         </is>
       </c>
       <c r="B213">
@@ -9151,7 +9151,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MS — Congênita</t>
+          <t>MS — Congenital</t>
         </is>
       </c>
       <c r="B214">
@@ -9193,7 +9193,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MS — Congênita</t>
+          <t>MS — Congenital</t>
         </is>
       </c>
       <c r="B215">
@@ -9232,7 +9232,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MT — Gestacional</t>
+          <t>MT — Gestational</t>
         </is>
       </c>
       <c r="B216">
@@ -9274,7 +9274,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MT — Gestacional</t>
+          <t>MT — Gestational</t>
         </is>
       </c>
       <c r="B217">
@@ -9316,7 +9316,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>MT — Gestacional</t>
+          <t>MT — Gestational</t>
         </is>
       </c>
       <c r="B218">
@@ -9358,7 +9358,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MT — Gestacional</t>
+          <t>MT — Gestational</t>
         </is>
       </c>
       <c r="B219">
@@ -9400,7 +9400,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MT — Gestacional</t>
+          <t>MT — Gestational</t>
         </is>
       </c>
       <c r="B220">
@@ -9439,7 +9439,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MT — Congênita</t>
+          <t>MT — Congenital</t>
         </is>
       </c>
       <c r="B221">
@@ -9481,7 +9481,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MT — Congênita</t>
+          <t>MT — Congenital</t>
         </is>
       </c>
       <c r="B222">
@@ -9523,7 +9523,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MT — Congênita</t>
+          <t>MT — Congenital</t>
         </is>
       </c>
       <c r="B223">
@@ -9565,7 +9565,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MT — Congênita</t>
+          <t>MT — Congenital</t>
         </is>
       </c>
       <c r="B224">
@@ -9607,7 +9607,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MT — Congênita</t>
+          <t>MT — Congenital</t>
         </is>
       </c>
       <c r="B225">
@@ -9646,7 +9646,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>GO — Gestacional</t>
+          <t>GO — Gestational</t>
         </is>
       </c>
       <c r="B226">
@@ -9688,7 +9688,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>GO — Gestacional</t>
+          <t>GO — Gestational</t>
         </is>
       </c>
       <c r="B227">
@@ -9727,7 +9727,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>GO — Congênita</t>
+          <t>GO — Congenital</t>
         </is>
       </c>
       <c r="B228">
@@ -9769,7 +9769,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>GO — Congênita</t>
+          <t>GO — Congenital</t>
         </is>
       </c>
       <c r="B229">
@@ -9811,7 +9811,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>GO — Congênita</t>
+          <t>GO — Congenital</t>
         </is>
       </c>
       <c r="B230">
@@ -9850,7 +9850,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>DF — Gestacional</t>
+          <t>DF — Gestational</t>
         </is>
       </c>
       <c r="B231">
@@ -9892,7 +9892,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>DF — Gestacional</t>
+          <t>DF — Gestational</t>
         </is>
       </c>
       <c r="B232">
@@ -9934,7 +9934,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DF — Gestacional</t>
+          <t>DF — Gestational</t>
         </is>
       </c>
       <c r="B233">
@@ -9973,7 +9973,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>DF — Congênita</t>
+          <t>DF — Congenital</t>
         </is>
       </c>
       <c r="B234">
@@ -10015,7 +10015,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DF — Congênita</t>
+          <t>DF — Congenital</t>
         </is>
       </c>
       <c r="B235">
@@ -10057,7 +10057,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DF — Congênita</t>
+          <t>DF — Congenital</t>
         </is>
       </c>
       <c r="B236">
@@ -10096,7 +10096,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional (sensibilidade 2012–2023)</t>
+          <t>Brasil — Gestational (sensibilidade 2012–2023)</t>
         </is>
       </c>
       <c r="B237">
@@ -10138,7 +10138,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional (sensibilidade 2012–2023)</t>
+          <t>Brasil — Gestational (sensibilidade 2012–2023)</t>
         </is>
       </c>
       <c r="B238">
@@ -10180,7 +10180,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional (sensibilidade 2012–2023)</t>
+          <t>Brasil — Gestational (sensibilidade 2012–2023)</t>
         </is>
       </c>
       <c r="B239">
@@ -10219,7 +10219,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (sensibilidade 2012–2023)</t>
+          <t>Brasil — Congenital (sensibilidade 2012–2023)</t>
         </is>
       </c>
       <c r="B240">
@@ -10261,7 +10261,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (sensibilidade 2012–2023)</t>
+          <t>Brasil — Congenital (sensibilidade 2012–2023)</t>
         </is>
       </c>
       <c r="B241">

--- a/R_analysis/output/tables/Tabela_Joinpoint_Completa.xlsx
+++ b/R_analysis/output/tables/Tabela_Joinpoint_Completa.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Macrorregião</t>
+          <t>Macro-region</t>
         </is>
       </c>
     </row>
